--- a/dev/StructureDefinition-ph-core-name.xlsx
+++ b/dev/StructureDefinition-ph-core-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T03:12:48+00:00</t>
+    <t>2026-03-18T09:54:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-name.xlsx
+++ b/dev/StructureDefinition-ph-core-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T09:54:13+00:00</t>
+    <t>2026-03-23T13:24:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-name.xlsx
+++ b/dev/StructureDefinition-ph-core-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T13:24:52+00:00</t>
+    <t>2026-03-25T02:48:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-name.xlsx
+++ b/dev/StructureDefinition-ph-core-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T02:48:03+00:00</t>
+    <t>2026-03-25T03:05:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-name.xlsx
+++ b/dev/StructureDefinition-ph-core-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:05:28+00:00</t>
+    <t>2026-03-25T03:10:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-name.xlsx
+++ b/dev/StructureDefinition-ph-core-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:10:05+00:00</t>
+    <t>2026-03-25T03:15:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-name.xlsx
+++ b/dev/StructureDefinition-ph-core-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:15:34+00:00</t>
+    <t>2026-03-25T03:26:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-name.xlsx
+++ b/dev/StructureDefinition-ph-core-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:26:10+00:00</t>
+    <t>2026-03-25T03:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-name.xlsx
+++ b/dev/StructureDefinition-ph-core-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:31:02+00:00</t>
+    <t>2026-03-25T03:34:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-name.xlsx
+++ b/dev/StructureDefinition-ph-core-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:34:45+00:00</t>
+    <t>2026-03-25T03:48:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-name.xlsx
+++ b/dev/StructureDefinition-ph-core-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:48:45+00:00</t>
+    <t>2026-03-25T03:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-name.xlsx
+++ b/dev/StructureDefinition-ph-core-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:54:03+00:00</t>
+    <t>2026-04-01T03:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-name.xlsx
+++ b/dev/StructureDefinition-ph-core-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T03:21:07+00:00</t>
+    <t>2026-04-01T03:34:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Philippines</t>
+    <t>Philippines (the)</t>
   </si>
   <si>
     <t>Description</t>

--- a/dev/StructureDefinition-ph-core-name.xlsx
+++ b/dev/StructureDefinition-ph-core-name.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T03:34:09+00:00</t>
+    <t>2026-04-01T03:44:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-name.xlsx
+++ b/dev/StructureDefinition-ph-core-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T03:44:59+00:00</t>
+    <t>2026-04-06T07:53:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-name.xlsx
+++ b/dev/StructureDefinition-ph-core-name.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="161">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-06T07:53:57+00:00</t>
+    <t>2026-04-08T04:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -341,22 +341,6 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>HumanName.extension:middleName</t>
-  </si>
-  <si>
-    <t>middleName</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://doh.gov.ph/fhir/ph-core/StructureDefinition/middle-name}
-</t>
-  </si>
-  <si>
-    <t>Middle Name</t>
-  </si>
-  <si>
-    <t>Extension to capture middle name information for a person</t>
-  </si>
-  <si>
     <t>HumanName.use</t>
   </si>
   <si>
@@ -450,10 +434,10 @@
 middle name</t>
   </si>
   <si>
-    <t>First Name</t>
-  </si>
-  <si>
-    <t>Given name.</t>
+    <t>First and middle names</t>
+  </si>
+  <si>
+    <t>First name (given[0]) and Middle Name (given[1]).</t>
   </si>
   <si>
     <t>If only initials are recorded, they may be used in place of the full name parts. Initials may be separated into multiple given names but often aren't due to paractical limitations.  This element is not called "first name" since given names do not always come first.</t>
@@ -825,12 +809,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM12"/>
+  <dimension ref="A1:AM11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="29.921875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="19.390625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="19.390625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="11.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -838,7 +822,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="60.86328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="8.609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1323,11 +1307,9 @@
         <v>106</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="C5" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
         <v>76</v>
       </c>
@@ -1342,10 +1324,10 @@
         <v>76</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>108</v>
@@ -1356,8 +1338,12 @@
       <c r="M5" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
+      <c r="N5" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O5" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="P5" t="s" s="2">
         <v>76</v>
       </c>
@@ -1381,13 +1367,13 @@
         <v>76</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="AA5" t="s" s="2">
         <v>76</v>
@@ -1405,36 +1391,36 @@
         <v>76</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>76</v>
+        <v>116</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>76</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1451,25 +1437,25 @@
         <v>76</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="O6" t="s" s="2">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="P6" t="s" s="2">
         <v>76</v>
@@ -1494,31 +1480,31 @@
         <v>76</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>118</v>
+        <v>76</v>
       </c>
       <c r="Y6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>119</v>
-      </c>
-      <c r="Z6" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>77</v>
@@ -1533,25 +1519,25 @@
         <v>84</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>123</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -1567,23 +1553,21 @@
         <v>76</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="K7" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="O7" t="s" s="2">
-        <v>128</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
         <v>76</v>
       </c>
@@ -1631,7 +1615,7 @@
         <v>76</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>77</v>
@@ -1646,32 +1630,32 @@
         <v>84</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>76</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>76</v>
@@ -1680,19 +1664,19 @@
         <v>76</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="K8" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1742,13 +1726,13 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>76</v>
@@ -1757,25 +1741,25 @@
         <v>84</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>140</v>
+        <v>76</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -1791,20 +1775,18 @@
         <v>76</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="K9" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>76</v>
@@ -1853,7 +1835,7 @@
         <v>76</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -1868,21 +1850,21 @@
         <v>84</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1902,16 +1884,16 @@
         <v>76</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="K10" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1962,7 +1944,7 @@
         <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -1977,13 +1959,13 @@
         <v>84</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11">
@@ -2002,7 +1984,7 @@
         <v>77</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>76</v>
@@ -2011,19 +1993,21 @@
         <v>76</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>90</v>
+        <v>154</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
+      <c r="O11" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="P11" t="s" s="2">
         <v>76</v>
       </c>
@@ -2077,7 +2061,7 @@
         <v>77</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>76</v>
@@ -2086,124 +2070,13 @@
         <v>84</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G12" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J12" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="K12" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="L12" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="N12" s="2"/>
-      <c r="O12" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="P12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q12" s="2"/>
-      <c r="R12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK12" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>165</v>
       </c>
     </row>
   </sheetData>

--- a/dev/StructureDefinition-ph-core-name.xlsx
+++ b/dev/StructureDefinition-ph-core-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T04:01:15+00:00</t>
+    <t>2026-04-13T08:21:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
